--- a/data/trans_orig/P1427-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2012</t>
+          <t>Población con diagnóstico de cataratas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,47 +767,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449495</t>
+          <t>449411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879707</t>
+          <t>879688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1075,97 +1075,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4963</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1044</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5224</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605012</t>
+          <t>605292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292118</t>
+          <t>1292057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671765</t>
+          <t>671754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680821</t>
+          <t>680819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698014</t>
+          <t>699552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1375795</t>
+          <t>1375731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388597</t>
+          <t>1388579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602589</t>
+          <t>604921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>605533</t>
+          <t>605764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613303</t>
+          <t>613305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1213943</t>
+          <t>1214038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1227748</t>
+          <t>1226825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>23393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>33981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412726</t>
+          <t>411760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425048</t>
+          <t>424272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424589</t>
+          <t>424407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440188</t>
+          <t>439371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>841927</t>
+          <t>843248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>862407</t>
+          <t>863265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15458</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35171</t>
+          <t>34816</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61507</t>
+          <t>61539</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277042</t>
+          <t>276610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295774</t>
+          <t>295183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317716</t>
+          <t>317212</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338538</t>
+          <t>338194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>602275</t>
+          <t>602243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628611</t>
+          <t>628966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35006</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60823</t>
+          <t>62632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>60897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96159</t>
+          <t>96335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208178</t>
+          <t>208572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230987</t>
+          <t>230700</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>328156</t>
+          <t>326347</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>353973</t>
+          <t>352394</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>542671</t>
+          <t>542495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578538</t>
+          <t>577933</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>53484</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87241</t>
+          <t>86156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75468</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116097</t>
+          <t>116739</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>136186</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188428</t>
+          <t>188561</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3339538</t>
+          <t>3340623</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3374369</t>
+          <t>3373295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3439001</t>
+          <t>3438359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3479630</t>
+          <t>3479505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6793449</t>
+          <t>6793316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6846306</t>
+          <t>6845691</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2016</t>
+          <t>Población con diagnóstico de cataratas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,97 +3711,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4054,97 +4054,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6125</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>985</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4646</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5899</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4918</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558898</t>
+          <t>557419</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149122</t>
+          <t>1148141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4397,97 +4397,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1766</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1766</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5527</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6909</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1766</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7043</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655859</t>
+          <t>656069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1323440</t>
+          <t>1323574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>646048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640664</t>
+          <t>639606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1285623</t>
+          <t>1286544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1294126</t>
+          <t>1294128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>20976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24627</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470372</t>
+          <t>469496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476962</t>
+          <t>476954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>475807</t>
+          <t>475873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490941</t>
+          <t>490928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>950140</t>
+          <t>950349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>966686</t>
+          <t>966918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21969</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48750</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312361</t>
+          <t>311861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326861</t>
+          <t>326705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344440</t>
+          <t>344688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>362403</t>
+          <t>363154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>663342</t>
+          <t>663250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>686876</t>
+          <t>687136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>27469</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27825</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55198</t>
+          <t>55818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44594</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77224</t>
+          <t>75627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229591</t>
+          <t>229529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244354</t>
+          <t>244776</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>344971</t>
+          <t>344351</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>372344</t>
+          <t>371566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>579943</t>
+          <t>581540</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>612573</t>
+          <t>611191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61224</t>
+          <t>63420</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100147</t>
+          <t>99565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93749</t>
+          <t>93876</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137383</t>
+          <t>139477</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3346202</t>
+          <t>3346005</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3368859</t>
+          <t>3369277</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3444395</t>
+          <t>3444977</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3483318</t>
+          <t>3481122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6801509</t>
+          <t>6799415</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6845143</t>
+          <t>6845016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2023</t>
+          <t>Población con diagnóstico de cataratas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,97 +6690,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2562</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17132</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2562</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11471</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>12812</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2562</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>14822</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301729</t>
+          <t>296068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698365</t>
+          <t>700375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,62 +7068,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2260</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>11486</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2260</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>11774</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411894</t>
+          <t>412134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923277</t>
+          <t>923565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,47 +7411,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>728</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6891</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2234</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>533099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534908</t>
+          <t>535809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541071</t>
+          <t>541072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070800</t>
+          <t>1070006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076049</t>
+          <t>1076051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35255</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>41962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>871947</t>
+          <t>872113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885433</t>
+          <t>885475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>677243</t>
+          <t>682603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>707225</t>
+          <t>707214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1559866</t>
+          <t>1558323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1589877</t>
+          <t>1589553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>23310</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44549</t>
+          <t>42900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534086</t>
+          <t>534413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>548722</t>
+          <t>549328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520450</t>
+          <t>520300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532629</t>
+          <t>532083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059298</t>
+          <t>1060947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1078245</t>
+          <t>1079667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22279</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38630</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63527</t>
+          <t>62974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29089</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93489</t>
+          <t>92083</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328623</t>
+          <t>328114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>344465</t>
+          <t>344085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>544408</t>
+          <t>544961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>591859</t>
+          <t>592785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>881190</t>
+          <t>882596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>945590</t>
+          <t>941867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39832</t>
+          <t>39015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59486</t>
+          <t>58185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72173</t>
+          <t>73135</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95643</t>
+          <t>96506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117259</t>
+          <t>117381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148133</t>
+          <t>147724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222409</t>
+          <t>223710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242063</t>
+          <t>242880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>330188</t>
+          <t>329325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>353658</t>
+          <t>352696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>559593</t>
+          <t>560002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>590467</t>
+          <t>590345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>80934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125938</t>
+          <t>125683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126816</t>
+          <t>124658</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181219</t>
+          <t>181666</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>228171</t>
+          <t>226231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>296101</t>
+          <t>294663</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3329238</t>
+          <t>3329493</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3373017</t>
+          <t>3374242</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3475158</t>
+          <t>3474711</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3529561</t>
+          <t>3531719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6815452</t>
+          <t>6816890</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6883382</t>
+          <t>6885322</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1427-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Edad-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449411</t>
+          <t>449959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879688</t>
+          <t>880003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605292</t>
+          <t>604995</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292057</t>
+          <t>1291075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671754</t>
+          <t>671632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680819</t>
+          <t>680807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>699552</t>
+          <t>697113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1375731</t>
+          <t>1376426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388579</t>
+          <t>1388473</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604921</t>
+          <t>601479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>605764</t>
+          <t>605048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613305</t>
+          <t>613298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1214038</t>
+          <t>1213348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1226825</t>
+          <t>1226940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23393</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>34522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>411760</t>
+          <t>411905</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424272</t>
+          <t>425222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424407</t>
+          <t>424611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439371</t>
+          <t>439999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>843248</t>
+          <t>842707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>863265</t>
+          <t>862011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>36791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61539</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276610</t>
+          <t>276209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295183</t>
+          <t>295666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317212</t>
+          <t>317205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338194</t>
+          <t>337605</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>602243</t>
+          <t>602725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628966</t>
+          <t>628313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62632</t>
+          <t>63201</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,47 +2840,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>77194</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>60121</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>95379</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>77194</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>60897</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>96335</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208572</t>
+          <t>208640</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230700</t>
+          <t>231880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326347</t>
+          <t>325778</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352394</t>
+          <t>352503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,47 +2953,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>561636</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>543451</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>578709</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>85,07%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>90,59%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>561636</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>542495</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>577933</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53484</t>
+          <t>52928</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86156</t>
+          <t>88371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>76098</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116739</t>
+          <t>117673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136186</t>
+          <t>136074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188561</t>
+          <t>187911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3340623</t>
+          <t>3338408</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3373295</t>
+          <t>3373851</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3438359</t>
+          <t>3437425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3479505</t>
+          <t>3479000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6793316</t>
+          <t>6793966</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6845691</t>
+          <t>6845803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557419</t>
+          <t>558582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1148141</t>
+          <t>1148118</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656069</t>
+          <t>655193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1323574</t>
+          <t>1324249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4775,47 +4775,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8455</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3186</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9471</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639606</t>
+          <t>640622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648077</t>
+          <t>648082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1286544</t>
+          <t>1286396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1294128</t>
+          <t>1294125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20976</t>
+          <t>21055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469496</t>
+          <t>469378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476954</t>
+          <t>476957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>475873</t>
+          <t>475794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490928</t>
+          <t>491386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>950349</t>
+          <t>950173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>966918</t>
+          <t>966365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>15294</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>35019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48842</t>
+          <t>50115</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311861</t>
+          <t>312766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326705</t>
+          <t>327066</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344688</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>363154</t>
+          <t>362468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>663250</t>
+          <t>661977</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>687136</t>
+          <t>686696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>27547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55818</t>
+          <t>54778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45976</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75627</t>
+          <t>74997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229529</t>
+          <t>229451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244776</t>
+          <t>244810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>344351</t>
+          <t>345391</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>371566</t>
+          <t>371997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>581540</t>
+          <t>582170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>611191</t>
+          <t>611488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>48016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63420</t>
+          <t>63030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93876</t>
+          <t>96676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>139477</t>
+          <t>141206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3346005</t>
+          <t>3346334</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3369277</t>
+          <t>3368858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3444977</t>
+          <t>3444382</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3481122</t>
+          <t>3481512</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6799415</t>
+          <t>6797686</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6845016</t>
+          <t>6842216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6833,27 +6833,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296068</t>
+          <t>349984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767841</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>700375</t>
+          <t>756375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7141,27 +7141,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421287</t>
+          <t>474457</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412134</t>
+          <t>462912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7211,27 +7211,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>975540</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923565</t>
+          <t>963207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>534980</t>
+          <t>619481</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>539565</t>
+          <t>619134</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535809</t>
+          <t>615154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541072</t>
+          <t>620737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1074545</t>
+          <t>1238615</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070006</t>
+          <t>1234777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076051</t>
+          <t>1240969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>534980</t>
+          <t>619481</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534980</t>
+          <t>619481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>534980</t>
+          <t>619481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076779</t>
+          <t>1240969</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076779</t>
+          <t>1240969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076779</t>
+          <t>1240969</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41962</t>
+          <t>24525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>880098</t>
+          <t>692918</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872113</t>
+          <t>686278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885475</t>
+          <t>697537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>700011</t>
+          <t>727837</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682603</t>
+          <t>721651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>707214</t>
+          <t>731419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1580110</t>
+          <t>1420754</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1558323</t>
+          <t>1412587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1589553</t>
+          <t>1427276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>26857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23310</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33613</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42900</t>
+          <t>48511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>543211</t>
+          <t>591085</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534413</t>
+          <t>581502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>549328</t>
+          <t>597207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>527023</t>
+          <t>586948</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520300</t>
+          <t>579702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532083</t>
+          <t>593357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1070234</t>
+          <t>1178033</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1060947</t>
+          <t>1165883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1079667</t>
+          <t>1186018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543610</t>
+          <t>606035</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543610</t>
+          <t>606035</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543610</t>
+          <t>606035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103847</t>
+          <t>1214394</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103847</t>
+          <t>1214394</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103847</t>
+          <t>1214394</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>40268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39161</t>
+          <t>43288</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62974</t>
+          <t>53686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>74330</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>61993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92083</t>
+          <t>89134</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>336970</t>
+          <t>374302</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328114</t>
+          <t>365076</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>344085</t>
+          <t>382164</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>568774</t>
+          <t>395420</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>544961</t>
+          <t>385022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>592785</t>
+          <t>402750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>905744</t>
+          <t>769722</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>882596</t>
+          <t>754918</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>941867</t>
+          <t>782059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607935</t>
+          <t>438708</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607935</t>
+          <t>438708</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607935</t>
+          <t>438708</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974679</t>
+          <t>844052</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974679</t>
+          <t>844052</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974679</t>
+          <t>844052</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>51171</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>41878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>62474</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>83761</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73135</t>
+          <t>78322</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96506</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>132458</t>
+          <t>140748</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117381</t>
+          <t>126437</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147724</t>
+          <t>156286</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>233198</t>
+          <t>258086</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223710</t>
+          <t>246783</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242880</t>
+          <t>267379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>342070</t>
+          <t>375032</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>329325</t>
+          <t>361103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352696</t>
+          <t>386287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>575268</t>
+          <t>633118</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>560002</t>
+          <t>617580</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>590345</t>
+          <t>647429</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707726</t>
+          <t>773866</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707726</t>
+          <t>773866</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707726</t>
+          <t>773866</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80934</t>
+          <t>92165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125683</t>
+          <t>128153</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124658</t>
+          <t>146671</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181666</t>
+          <t>186357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>226231</t>
+          <t>250908</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>294663</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3349732</t>
+          <t>3418123</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3329493</t>
+          <t>3399589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3374242</t>
+          <t>3435577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3499585</t>
+          <t>3565504</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3474711</t>
+          <t>3544574</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3531719</t>
+          <t>3584260</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6849317</t>
+          <t>6983626</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6816890</t>
+          <t>6954580</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6885322</t>
+          <t>7007764</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
